--- a/DateBase/orders/Nha Thu_2026-5-20.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-20.xlsx
@@ -951,6 +951,9 @@
       <c r="G2" t="str">
         <v>05050105555510555105105555101510515141320959551520101010105510555555555101015</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
